--- a/data/Escenarios_DCH_agosto/Costo_variable/Swap_variable_3estaciones_320kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_agosto/Costo_variable/Swap_variable_3estaciones_320kW/elmo_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_costos_nuevos\Costo_variable\Swap_variable_3estaciones_320kW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_agosto\Costo_variable\Swap_variable_3estaciones_320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAB653D-08D6-403D-BCB2-B830D2C7F460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8D45F0-0456-43DF-9140-B088A6453DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3578,7 +3578,7 @@
         <v>38221</v>
       </c>
       <c r="E3">
-        <v>16725</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>5733</v>
@@ -3613,7 +3613,7 @@
         <v>38221</v>
       </c>
       <c r="E4">
-        <v>16725</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>5733</v>
@@ -3648,7 +3648,7 @@
         <v>38221</v>
       </c>
       <c r="E5">
-        <v>16725</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>5733</v>
